--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/358FL_15A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/358FL_15A.xlsx
@@ -11457,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11559,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -11627,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
